--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>First in line of succession -- Oregon has NO Lieutenant Governor. Tobias Read (2024 cycle). Pending.</t>
+          <t>First in line of succession -- Oregon has NO Lieutenant Governor. BUILT (PR #171): Tobias Read, 2024 general election (SOS certified abstract: 1,166,447); sworn in Jan 6, 2025.</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Elizabeth Steiner (2024 cycle). Pending.</t>
+          <t>BUILT (PR #171): Elizabeth Steiner, 2024 general election (SOS certified abstract: 1,050,119); sworn in Jan 6, 2025.</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Dan Rayfield, took office Dec 31, 2024 (2024 cycle). Pending.</t>
+          <t>BUILT (PR #171): Dan Rayfield, 2024 general election (SOS certified abstract: 1,156,489); sworn in Dec 31, 2024 on the early resignation of Ellen Rosenblum.</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Christina Stephenson (2022 cycle). Pending.</t>
+          <t>BUILT (PR #171): Christina Stephenson, 2022 general election (SOS certified abstract: 916,455, nonpartisan); assumed office Jan 2, 2023. Re-elected in the May 2026 primary (majority in May under the nonpartisan rule).</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15594,6 +15594,33 @@
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Statewide executive completed on PR #171: Secretary of State (Read), State Treasurer (Steiner), and Attorney General (Rayfield) built from the certified Nov 5, 2024 abstract, and Commissioner of Labor and Industries (Stephenson) from the certified Nov 8, 2022 abstract -- each as org + post + new person + membership + election contest, cross-checked against the CivicMirror API's 2026 races. All 5 elected statewide offices now built. Validation on the OR tree PASSED, 0 errors. Also: the SOS retired the old sos.oregon.gov abstract PDF paths; abstracts are now published via the Oregon State Archives records system (records.sos.state.or.us), and the Governor-step source URLs were repaired to the current official location.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Government Structure, Status Log</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); Multnomah County elected-officials page; BOLI commissioner page; CivicMirror API</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>

--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Government Structure" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Municipalities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="School Districts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Counties" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Office Titles (Ref)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Status Log" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Open Issues" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Government Structure" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Municipalities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School Districts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counties" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Titles (Ref)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Issues" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Structure determined 2026-10-23 (issue #170 first pass). Federal tier built; Governor built (PR #171); all other tiers pending in Walter's order.</t>
+          <t>Structure determined 2026-10-23 (issue #170 first pass). Federal tier built; statewide executive and legislative tiers built (PR #171); judicial, county, municipal, then schools / ESDs / special districts pending in Walter's order.</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Legislative pass (second in Walter's order). Each Senate district = exactly 2 House districts.</t>
+          <t>BUILT (PR #171): all 30 district jurisdictions + posts + holders from the certified SOS abstracts (2024 class: Districts 1, 2, 5, 9, 12, 14, 18, 21, 22, 23, 25, 27, 28, 29, 30; 2022 class: the other 15, plus the District 18 two-year-term contest). Mid-term appointments modeled in Districts 13, 17, 26. Each Senate district = exactly 2 House districts.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Legislative pass. All 60 seats up Nov 3, 2026.</t>
+          <t>BUILT (PR #171): all 60 district jurisdictions + posts + holders from the certified 2024 SOS abstract. Mid-term appointments modeled in Districts 26, 34, 48, 51 (District 34: the re-elected winner resigned before the term began -- candidacy recorded, no membership). All 60 seats up Nov 3, 2026.</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15607,20 +15607,47 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Legislative pass built on PR #171: 90 district jurisdictions + organizations + posts (Senate 30, House 60), 93 new people, 96 memberships, and 91 legislative contests appended to the 2022 and 2024 general election files, all from the certified SOS Abstracts of Votes with county-row sums matching the printed totals; CivicMirror API 2026 race list used as the Senate-class cross-check. Seven mid-term successions modeled (SD13, SD17, SD26, HD26, HD34, HD48, HD51). Validation on the OR tree PASSED, 0 errors, 10 warnings (9 pre-existing baseline + 1 by-design winner-not-seated for HD34).</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Government Structure, Status Log</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); county commission appointment releases (Washington, Multnomah, Clackamas); Oregon Legislature</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>Statewide executive completed on PR #171: Secretary of State (Read), State Treasurer (Steiner), and Attorney General (Rayfield) built from the certified Nov 5, 2024 abstract, and Commissioner of Labor and Industries (Stephenson) from the certified Nov 8, 2022 abstract -- each as org + post + new person + membership + election contest, cross-checked against the CivicMirror API's 2026 races. All 5 elected statewide offices now built. Validation on the OR tree PASSED, 0 errors. Also: the SOS retired the old sos.oregon.gov abstract PDF paths; abstracts are now published via the Oregon State Archives records system (records.sos.state.or.us), and the Governor-step source URLs were repaired to the current official location.</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Government Structure, Status Log</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); Multnomah County elected-officials page; BOLI commissioner page; CivicMirror API</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>

--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1002,32 +1002,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>State Senate</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Elected</t>
+          <t>Elected (nonpartisan)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>4 years (staggered, 15 per cycle)</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30 districts</t>
+          <t>7 positions</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Or. Const. Art. IV</t>
+          <t>Or. Const. Art. VII; ORS 2.020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>BUILT (PR #171): all 30 district jurisdictions + posts + holders from the certified SOS abstracts (2024 class: Districts 1, 2, 5, 9, 12, 14, 18, 21, 22, 23, 25, 27, 28, 29, 30; 2022 class: the other 15, plus the District 18 two-year-term contest). Mid-term appointments modeled in Districts 13, 17, 26. Each Senate district = exactly 2 House districts.</t>
+          <t>BUILT (PR #171, appellate tier of the judicial pass): all 7 positions + holders from the certified SOS Abstracts of Votes (2020/2022/2024, primary + general). Appointee-then-elected justices (Bushong Pos 1, James Pos 7, Masih Pos 5, DeHoog Pos 6) carry appointed + elected memberships; departed 2020 winners Balmer (Pos 1) and Walters (Pos 7) carry ended memberships. Chief Justice: Meagan Flynn (Pos 3), since Jan 2023.</t>
         </is>
       </c>
     </row>
@@ -1039,44 +1039,44 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>State House of Representatives</t>
+          <t>Court of Appeals</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Elected</t>
+          <t>Elected (nonpartisan)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60 districts</t>
+          <t>13 positions</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Or. Const. Art. IV</t>
+          <t>ORS 2.540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>BUILT (PR #171): all 60 district jurisdictions + posts + holders from the certified 2024 SOS abstract. Mid-term appointments modeled in Districts 26, 34, 48, 51 (District 34: the re-elected winner resigned before the term began -- candidacy recorded, no membership). All 60 seats up Nov 3, 2026.</t>
+          <t>BUILT (PR #171, appellate tier of the judicial pass): all 13 positions + holders from the certified SOS abstracts. Appointee-then-elected judges (Pagan Pos 8, Kamins Pos 9, Joyce Pos 11) carry appointed + elected memberships; departed 2020 winner DeVore (Pos 11) carries an ended membership (year-precision end).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>State</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Tax Court</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1091,29 +1091,29 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7 justices, statewide</t>
+          <t>1 judge</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Or. Const. Art. VII; ORS ch. 2</t>
+          <t>ORS 305.400s</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Judicial pass -- sits directly under the legislative pass (Walter, 2026-10-23).</t>
+          <t>BUILT (PR #171, appellate tier of the judicial pass): Judge Robert Manicke, re-elected in the May 21, 2024 primary (566,517, certified abstract). The Tax Court race appears in the primary abstract under 'Judge of the Oregon Tax Court' with no position line.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>State</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Court of Appeals</t>
+          <t>Circuit Courts</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13 judges, statewide</t>
+          <t>27 judicial districts, ~180 positions</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ORS ch. 2</t>
+          <t>Or. Const. Art. VII; ORS 3.012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Judicial pass.</t>
+          <t>NOT BUILT YET (judicial pass, next slice): 181 district-positions have a parsed 2020-2024 race in the six certified abstracts; reconciliation against OJD rosters + appointment announcements is the next step.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>County / justice districts</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tax Court</t>
+          <t>Justices of the Peace</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1165,91 +1165,91 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1 judge, statewide</t>
+          <t>per justice district</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>ORS ch. 305</t>
+          <t>ORS 51.210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Judicial pass.</t>
+          <t>NOT BUILT YET (judicial pass, last slice): county-authorized and outside the Oregon Judicial Department; the Jurisdiction Factory lists 20 seats (lead layer only).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>State</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Circuit Courts</t>
+          <t>State Senate</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Elected (nonpartisan)</t>
+          <t>Elected</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>4 years (staggered, 15 per cycle)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27 judicial districts</t>
+          <t>30 districts</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>ORS ch. 3</t>
+          <t>Or. Const. Art. IV</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Judicial pass. District lines follow county boundaries (some multi-county).</t>
+          <t>BUILT (PR #171): all 30 district jurisdictions + posts + holders from the certified SOS abstracts (2024 class: Districts 1, 2, 5, 9, 12, 14, 18, 21, 22, 23, 25, 27, 28, 29, 30; 2022 class: the other 15, plus the District 18 two-year-term contest). Mid-term appointments modeled in Districts 13, 17, 26. Each Senate district = exactly 2 House districts.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>State</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Justice of the Peace (Justice Courts)</t>
+          <t>State House of Representatives</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Elected (nonpartisan)</t>
+          <t>Elected</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1 per justice district</t>
+          <t>60 districts</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>ORS 51.210</t>
+          <t>Or. Const. Art. IV</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>County-authorized courts, NOT part of the Oregon Judicial Department. Factory models 20 seats -- verify per county (Open Issues #4). County Court judicial functions in County Court counties sit here too.</t>
+          <t>BUILT (PR #171): all 60 district jurisdictions + posts + holders from the certified 2024 SOS abstract. Mid-term appointments modeled in Districts 26, 34, 48, 51 (District 34: the re-elected winner resigned before the term began -- candidacy recorded, no membership). All 60 seats up Nov 3, 2026.</t>
         </is>
       </c>
     </row>
@@ -1261,229 +1261,229 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Municipal court judges</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>APPOINTED -- out of elected scope</t>
+          <t>Elected (nonpartisan)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>7 justices, statewide</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>City charters</t>
+          <t>Or. Const. Art. VII; ORS ch. 2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Excluded.</t>
+          <t>Judicial pass -- sits directly under the legislative pass (Walter, 2026-10-23).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Board of County Commissioners</t>
+          <t>Court of Appeals</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Elected</t>
+          <t>Elected (nonpartisan)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>4 years (staggered)</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Usually 3 or 5, by numbered positions</t>
+          <t>13 judges, statewide</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>ORS 204.013 / 204.017</t>
+          <t>ORS ch. 2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The governing body in most of the 36 counties. County pass (fourth).</t>
+          <t>Judicial pass.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>County Court (County Judge + 2 Commissioners)</t>
+          <t>Tax Court</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Elected</t>
+          <t>Elected (nonpartisan)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>6 years (Judge) / 4 years (Commissioners)</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Eastern counties (factory: 6 -- Gilliam, Grant, Harney, Malheur, Sherman, Wheeler)</t>
+          <t>1 judge, statewide</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>ORS ch. 204 / 205</t>
+          <t>ORS ch. 305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>OJD describes County Courts in SEVEN eastern counties -- Morrow is the divergence (Open Issues #1). The County Judge also carries judicial functions.</t>
+          <t>Judicial pass.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sheriff / County Clerk / County Assessor / County Treasurer</t>
+          <t>Circuit Courts</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Elected</t>
+          <t>Elected (nonpartisan)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1 per county each (where the office exists)</t>
+          <t>27 judicial districts</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ORS 204.005</t>
+          <t>ORS ch. 3</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charters (9 counties) can combine, appoint, or replace offices (e.g. an elected County Auditor in 2 factory counties) -- per-county charter check.</t>
+          <t>Judicial pass. District lines follow county boundaries (some multi-county).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>County Surveyor</t>
+          <t>Justice of the Peace (Justice Courts)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Elected where not made appointive</t>
+          <t>Elected (nonpartisan)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1 per county (conditional)</t>
+          <t>1 per justice district</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>ORS 204.005</t>
+          <t>ORS 51.210</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Only where the county charter/ordinance has not made it appointed. Factory models 24.</t>
+          <t>County-authorized courts, NOT part of the Oregon Judicial Department. Factory models 20 seats -- verify per county (Open Issues #4). County Court judicial functions in County Court counties sit here too.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>District Attorney</t>
+          <t>Municipal court judges</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Elected</t>
+          <t>APPOINTED -- out of elected scope</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>--</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1 per county (36)</t>
+          <t>--</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>ORS 8.610</t>
+          <t>City charters</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Factory carries only 34 -- Clatsop and Hood River are factory gaps (Open Issues #2-3).</t>
+          <t>Excluded.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>County</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Mayor + City Council</t>
+          <t>Board of County Commissioners</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1493,34 +1493,34 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Charter terms (2-4 years typical)</t>
+          <t>4 years (staggered)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240 cities</t>
+          <t>Usually 3 or 5, by numbered positions</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>City charters (all home-rule)</t>
+          <t>ORS 204.013 / 204.017</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Every Oregon city is a home-rule charter city -- mayor/council set, titles, and terms come from each city charter. Municipal pass (fifth), alphabetical batches of 10, factory as lead layer.</t>
+          <t>The governing body in most of the 36 counties. County pass (fourth).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>County</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>School district boards</t>
+          <t>County Court (County Judge + 2 Commissioners)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1530,39 +1530,39 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>6 years (Judge) / 4 years (Commissioners)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>District count to verify against ODE</t>
+          <t>Eastern counties (factory: 6 -- Gilliam, Grant, Harney, Malheur, Sherman, Wheeler)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>ORS ch. 332</t>
+          <t>ORS ch. 204 / 205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Elections in May of odd years. School pass runs LAST (Walter, 2026-10-23).</t>
+          <t>OJD describes County Courts in SEVEN eastern counties -- Morrow is the divergence (Open Issues #1). The County Judge also carries judicial functions.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>County</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Education Service District boards</t>
+          <t>Sheriff / County Clerk / County Assessor / County Treasurer</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>MIXED -- elected/appointed by district</t>
+          <t>Elected</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1572,52 +1572,237 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19 ESDs</t>
+          <t>1 per county each (where the office exists)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ORS ch. 334</t>
+          <t>ORS 204.005</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Needs a #158-style per-district classification in the school pass.</t>
+          <t>Home-rule charters (9 counties) can combine, appoint, or replace offices (e.g. an elected County Auditor in 2 factory counties) -- per-county charter check.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>County Surveyor</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Elected where not made appointive</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1 per county (conditional)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>ORS 204.005</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Only where the county charter/ordinance has not made it appointed. Factory models 24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>District Attorney</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Elected</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1 per county (36)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>ORS 8.610</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Factory carries only 34 -- Clatsop and Hood River are factory gaps (Open Issues #2-3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Mayor + City Council</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Elected</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Charter terms (2-4 years typical)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>240 cities</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>City charters (all home-rule)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Every Oregon city is a home-rule charter city -- mayor/council set, titles, and terms come from each city charter. Municipal pass (fifth), alphabetical batches of 10, factory as lead layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>School district boards</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Elected</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>District count to verify against ODE</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>ORS ch. 332</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Elections in May of odd years. School pass runs LAST (Walter, 2026-10-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Education Service District boards</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>MIXED -- elected/appointed by district</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>19 ESDs</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>ORS ch. 334</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Needs a #158-style per-district classification in the school pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>Special districts</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Fire / water / port / park / library / SWCD and other special district boards</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Mostly elected boards</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Varies</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>~1,035 districts (OCCMA count)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>ORS ch. 198 et seq.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Deferred to the final pass with schools. The restricted-franchise rule (Walter, 2026-10-15) applies district by district: a body the general public cannot vote for is out of scope. Port of Portland commissioners are Governor-appointed -- out.</t>
         </is>
@@ -15454,7 +15639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15580,17 +15765,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Walter's order rulings recorded: judicial sits directly under legislative; schools / ESDs / special districts run after the municipal pass; XLSX workbook ruled IN (this file). JUD / ESD / SPC settled; no scope items left parked.</t>
+          <t>Judicial pass, appellate tier built on PR #171 (commit 9807891): state judiciary jurisdiction + Supreme Court (7), Court of Appeals (13) and Tax Court (1) organizations, posts, holders and 24 contests across six election files (new 2020 primary, 2020 general, 2022 primary, 2024 primary files; contests appended to the 2022/2024 general files), all from the certified SOS Abstracts of Votes. Oregon judicial races are decided at the May primary on a majority, so the primary abstracts carry most of the bench. Seven holders carry appointed + elected membership pairs (Bushong, James, Masih, DeHoog, Pagan, Kamins, Joyce) and three departed 2020 winners carry ended memberships (Balmer, Walters, DeVore). Validation PASSED, 0 errors, 10 warnings (9 baseline + HD34 by-design). Circuit Courts and Justices of the Peace remain in the judicial pass.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>README, Government Structure, Status Log</t>
+          <t>Government Structure, Status Log</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Walter, via #170 side chat 2026-10-23</t>
+          <t>SOS Abstracts of Votes 2020-2024 (Archives uris 13735448-13735458); Governor's appointment releases (Brown Dec 2022 / Jan 19, 2022; Kotek Aug 16, 2023); OSB Capitol Insider (Balmer/Walters retirements)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15607,17 +15792,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Legislative pass built on PR #171: 90 district jurisdictions + organizations + posts (Senate 30, House 60), 93 new people, 96 memberships, and 91 legislative contests appended to the 2022 and 2024 general election files, all from the certified SOS Abstracts of Votes with county-row sums matching the printed totals; CivicMirror API 2026 race list used as the Senate-class cross-check. Seven mid-term successions modeled (SD13, SD17, SD26, HD26, HD34, HD48, HD51). Validation on the OR tree PASSED, 0 errors, 10 warnings (9 pre-existing baseline + 1 by-design winner-not-seated for HD34).</t>
+          <t>Walter's order rulings recorded: judicial sits directly under legislative; schools / ESDs / special districts run after the municipal pass; XLSX workbook ruled IN (this file). JUD / ESD / SPC settled; no scope items left parked.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Government Structure, Status Log</t>
+          <t>README, Government Structure, Status Log</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); county commission appointment releases (Washington, Multnomah, Clackamas); Oregon Legislature</t>
+          <t>Walter, via #170 side chat 2026-10-23</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15634,20 +15819,47 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Legislative pass built on PR #171: 90 district jurisdictions + organizations + posts (Senate 30, House 60), 93 new people, 96 memberships, and 91 legislative contests appended to the 2022 and 2024 general election files, all from the certified SOS Abstracts of Votes with county-row sums matching the printed totals; CivicMirror API 2026 race list used as the Senate-class cross-check. Seven mid-term successions modeled (SD13, SD17, SD26, HD26, HD34, HD48, HD51). Validation on the OR tree PASSED, 0 errors, 10 warnings (9 pre-existing baseline + 1 by-design winner-not-seated for HD34).</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Government Structure, Status Log</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); county commission appointment releases (Washington, Multnomah, Clackamas); Oregon Legislature</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>Statewide executive completed on PR #171: Secretary of State (Read), State Treasurer (Steiner), and Attorney General (Rayfield) built from the certified Nov 5, 2024 abstract, and Commissioner of Labor and Industries (Stephenson) from the certified Nov 8, 2022 abstract -- each as org + post + new person + membership + election contest, cross-checked against the CivicMirror API's 2026 races. All 5 elected statewide offices now built. Validation on the OR tree PASSED, 0 errors. Also: the SOS retired the old sos.oregon.gov abstract PDF paths; abstracts are now published via the Oregon State Archives records system (records.sos.state.or.us), and the Governor-step source URLs were repaired to the current official location.</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Government Structure, Status Log</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); Multnomah County elected-officials page; BOLI commissioner page; CivicMirror API</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>

--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Government Structure" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Municipalities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School Districts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counties" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Titles (Ref)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Log" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Issues" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Government Structure" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Municipalities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="School Districts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Counties" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Office Titles (Ref)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Status Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Open Issues" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27 judicial districts, ~180 positions</t>
+          <t>27 judicial districts, 186 positions</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Or. Const. Art. VII; ORS 3.012</t>
+          <t>Or. Const. Art. VII; ORS 3.010 / 3.012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>NOT BUILT YET (judicial pass, next slice): 181 district-positions have a parsed 2020-2024 race in the six certified abstracts; reconciliation against OJD rosters + appointment announcements is the next step.</t>
+          <t>BUILT (PR #171, circuit tier of the judicial pass): all 27 district jurisdictions + court organizations, all 186 posts (the OJD judges-directory count -- the directory runs ahead of the ORS 3.012 text in Districts 1, 2, 5, 16 and 20, which have recently created judgeships), 200 deciding contests from the certified SOS abstracts appended to the six election files, and elected memberships for the 169 seats whose holder's class-aligned win fully determines the seating. Memberships at 17 seats are held for the research step (5 new-judgeship appointees, 4 departure-&gt;appointment seats, 4 class contradictions, 3 vacancies, 1 surname-masked succession at 20-14); the 12 winner-not-seated validation warnings are that queue.</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15846,20 +15846,47 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Judicial pass, Circuit Courts built on PR #171 (commit 696e17f): 27 judicial-district jurisdictions + circuit court organizations (ORS 3.010/3.012), 186 posts -- the Oregon Judicial Department judges-directory count, which runs ahead of the ORS 3.012 text in Districts 1 (11), 2 (17), 5 (13), 16 (6) and 20 (16) with recently created judgeships; raced position numbers match directory numbers everywhere, so no renumbering. 200 deciding contests appended to the six election files (indecisive primaries feeding a November runoff are not separate contests); candidacies for all 200 winners; elected memberships for the 169 seats whose sitting judge's class-aligned certified win fully determines the seating (term start = first Monday in January: 2021-01-04 / 2023-01-02 / 2025-01-06). Three winners already on file (Bushong, Jacquot, McLane) had candidacies appended to their existing person records. HELD for the research step (Walter's direction): memberships at 17 seats -- new-judgeship appointees 2-16, 2-17, 5-12, 5-13, 16-6; departure-&gt;appointment seats 4-18, 4-34, 5-6, 13-2; class contradictions 2-14, 4-6, 5-5, 20-1; vacancies 4-2, 4-14, 11-3; surname-masked succession 20-14 (Miranda Summer won the 2022 race, Maalik M. Summer holds the seat). Validation PASSED, 0 errors, 22 warnings (10 baseline + the 12 held-seat winner-not-seated warnings, which are the research queue). Remaining in the judicial pass: Justices of the Peace.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Government Structure, Status Log</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>SOS Abstracts of Votes 2020-2024 (Archives uris 13735448-13735458); Oregon Judicial Department judges directory (courts.oregon.gov, accessed 2026-10-23); ORS 3.010/3.012 (oregonlegislature.gov)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>Statewide executive completed on PR #171: Secretary of State (Read), State Treasurer (Steiner), and Attorney General (Rayfield) built from the certified Nov 5, 2024 abstract, and Commissioner of Labor and Industries (Stephenson) from the certified Nov 8, 2022 abstract -- each as org + post + new person + membership + election contest, cross-checked against the CivicMirror API's 2026 races. All 5 elected statewide offices now built. Validation on the OR tree PASSED, 0 errors. Also: the SOS retired the old sos.oregon.gov abstract PDF paths; abstracts are now published via the Oregon State Archives records system (records.sos.state.or.us), and the Governor-step source URLs were repaired to the current official location.</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Government Structure, Status Log</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); Multnomah County elected-officials page; BOLI commissioner page; CivicMirror API</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>

--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>per justice district</t>
+          <t>22 seats in 21 counties (Douglas has 2 districts)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>NOT BUILT YET (judicial pass, last slice): county-authorized and outside the Oregon Judicial Department; the Jurisdiction Factory lists 20 seats (lead layer only).</t>
+          <t>BUILT (PR #171, JP slice of the judicial pass, commit 2beb5a1): one Justice Court organization per county on the existing county jurisdictions, 22 posts, 28 new people, 25 memberships, 14 contests in 13 new county election files from county official results (the state abstracts carry no JP races). Denominator = SOS Blue Book county pages: 22 seats -- the factory's 20 missed Hood River and Union. Three holders are gubernatorial appointees (Rastetter/Clackamas 2026, Hayter/Gilliam 2024, Joseph/Union 2026); Union's 2022 winner Dall is held without a membership (resignation date undocumented -- the tier's one winner-not-seated warning). Blue Book term years were wrong for Hood River, Klamath, Sherman and Tillamook and were overridden by county documents, disclosed in the source notes. Certified totals not posted online for Baker, Harney, Wheeler, Klamath, Lane, Linn, Sherman and Gilliam-2020 are clerk-request items.</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>County-authorized courts, NOT part of the Oregon Judicial Department. Factory models 20 seats -- verify per county (Open Issues #4). County Court judicial functions in County Court counties sit here too.</t>
+          <t>County-authorized courts, NOT part of the Oregon Judicial Department. Verified denominator is 22 seats in 21 counties (Blue Book county pages) -- the factory's 20 missed Hood River and Union; built in the judicial pass (PR #171). County Court judicial functions in County Court counties sit here too.</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -15488,76 +15488,76 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Official directory of state/county officials and government structure.</t>
+          <t>Official directory of state/county officials and government structure; its county pages list each county's officers including Justices of the Peace.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>USED -- JP denominator (all 36 county pages)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Directory aid; election facts still come from the certified abstracts.</t>
+          <t>Directory aid; election facts come from certified results. The Blue Book is stale for Clackamas (pre-retirement) and its term years were wrong for Hood River, Klamath, Sherman and Tillamook -- county documents governed there, disclosed in the repo source notes.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Oregon Judicial Department</t>
+          <t>County clerks' certified election results (per county)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>County</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Official (state)</t>
+          <t>Official (county)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>PDF download / web</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.courts.oregon.gov/about/Pages/default.aspx</t>
+          <t>Per-county clerk pages</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Court structure: Supreme Court, Court of Appeals, Tax Court, 27 circuit-court districts; County Court counties.</t>
+          <t>Certified Justice of the Peace results, which the state abstracts do not carry: Columbia, Douglas, Grant, Malheur, Tillamook, Clackamas, Deschutes, Hood River, Marion, Washington, Jackson, Morrow, Union documents used for the JP tier.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>USED -- structure pass (issue #170)</t>
+          <t>USED -- JP contests</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Justice Courts are county-authorized and outside the OJD -- verify JPs per county.</t>
+          <t>Retrieval gaps (Laserfiche/PDF viewers) were pulled in a live browser. Eight seats have no certified total posted online (clerk-request items).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>League of Oregon Cities</t>
+          <t>Oregon Judicial Department</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Association</t>
+          <t>Official (state)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -15567,62 +15567,104 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>https://www.orcities.org/about/how-we-work</t>
+          <t>https://www.courts.oregon.gov/about/Pages/default.aspx</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>City count (241 incorporated cities incl. the former Auburn listing question; 240 govern after the Auburn correction) and charter-city orientation.</t>
+          <t>Court structure: Supreme Court, Court of Appeals, Tax Court, 27 circuit-court districts; County Court counties.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>USED -- locate/verify only</t>
+          <t>USED -- structure pass (issue #170)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Association source: used to locate and verify, NOT as source of record (mirrors the MS MML / VT VLCT rule).</t>
+          <t>Justice Courts are county-authorized and outside the OJD -- verify JPs per county.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>League of Oregon Cities</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Association</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.orcities.org/about/how-we-work</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>City count (241 incorporated cities incl. the former Auburn listing question; 240 govern after the Auburn correction) and charter-city orientation.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>USED -- locate/verify only</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Association source: used to locate and verify, NOT as source of record (mirrors the MS MML / VT VLCT rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Creyton Loud -- OR Jurisdiction Factory v0.1 (Google Sheet)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>County / Municipal</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>NOT official -- lead layer</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Sheets API / export</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>https://docs.google.com/spreadsheets/d/15A-_pC85UZevw2bInfn4bG-3Zuya_KwFJl_cm1TWMXw</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>277 jurisdictions (36 counties, 240 cities), 1,844 offices, 1,809 people/role terms, 1,485 evidence rows -- county and municipal tiers only.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>USED -- concordance posted to #170 (2026-10-23)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Creyton Loud's file, shared for collaboration; READ-ONLY. Verify every roster against the official source its evidence rows cite before minting; flag divergences on #170.</t>
         </is>
@@ -15639,7 +15681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15873,20 +15915,47 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Judicial pass, Justices of the Peace built on PR #171 (commit 2beb5a1), completing the judicial tier's build phase: 21 Justice Court organizations (on the existing county jurisdictions), 22 posts, 28 new people, 25 memberships, and 13 new county election files with 14 contests from county official results. Denominator from the SOS Blue Book county pages: 22 seats in 21 counties (Douglas has two districts) -- the factory's 20 seats missed Hood River and Union, and the Oregon Law Commission's '22 justice courts' agrees. The state abstracts carry no JP races and JP races are decided at the May primary on a majority (only Jackson and Union were November decisions). Three sitting JPs are gubernatorial appointees: Rastetter (Clackamas, effective 2026-01-01 on Brisbin's retirement -- factory right, Blue Book stale), Hayter (Gilliam, June 2024; the 2020 holder was Patnode), Joseph (Union, 2026-02-01). Union's 2022 winner Dall (7,938) carries a candidacy + contest but no membership -- his resignation date is undocumented, and the resulting winner-not-seated warning is the hold. Joe Charter's Nov 2024 JP win (43,176) was appended to his existing circuit-court person record (he left Circuit 1-8 in 2024). Blue Book term years overridden by county documents for Hood River (Harvey elected May 2022, Cascade Locks district), Klamath, Sherman and Tillamook (Connell re-elected May 2024; separate 2019-2024 membership from the county's 2018 order). Validation PASSED, 0 errors, 23 warnings (22 prior + the Dall hold). Remaining in the judicial pass: the circuit research items (17 seats).</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Government Structure, Status Log, Open Issues</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SOS Blue Book county pages (sos.oregon.gov); county clerks' certified results (Columbia, Douglas, Grant, Malheur, Tillamook, Clackamas, Deschutes, Hood River, Marion, Washington, Jackson, Union); Clackamas County releases and minutes (Rastetter appointment); Sherman County elected-officials list; Tillamook County BOC order (2018) and ACFRs</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>Statewide executive completed on PR #171: Secretary of State (Read), State Treasurer (Steiner), and Attorney General (Rayfield) built from the certified Nov 5, 2024 abstract, and Commissioner of Labor and Industries (Stephenson) from the certified Nov 8, 2022 abstract -- each as org + post + new person + membership + election contest, cross-checked against the CivicMirror API's 2026 races. All 5 elected statewide offices now built. Validation on the OR tree PASSED, 0 errors. Also: the SOS retired the old sos.oregon.gov abstract PDF paths; abstracts are now published via the Oregon State Archives records system (records.sos.state.or.us), and the Governor-step source URLs were repaired to the current official location.</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Government Structure, Status Log</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); Multnomah County elected-officials page; BOLI commissioner page; CivicMirror API</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>
@@ -16021,7 +16090,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Verification owed</t>
+          <t>Verification owed -- RESOLVED 2026-10-23</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -16031,12 +16100,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The factory models 20 JP seats. Justice districts are created by county order and justice courts are not part of the Oregon Judicial Department, so there is no single official roster to check the 20 against yet.</t>
+          <t>The factory modeled 20 JP seats; the verified denominator is 22 seats in 21 counties (SOS Blue Book county pages, corroborated by the Oregon Law Commission's count of 22 justice courts). The factory missed Hood River (Harvey) and Union (Joseph) entirely and was right against a stale Blue Book in Clackamas (Rastetter's appointment). All 22 seats are built (PR #171, commit 2beb5a1).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Per-county ordinances / SOS records during the judicial pass; reconcile the seat count before minting.</t>
+          <t>Done. Leftovers in the research queue: certified totals not posted online for 8 seats (clerk requests), Dall's resignation date (Union), Joseph's appointment announcement, Charter's circuit departure date, and whether Hood River has a second justice district.</t>
         </is>
       </c>
     </row>

--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36 counties -- jurisdiction scaffolds only; county pass runs fourth, factory as lead layer.</t>
+          <t>36 counties -- BUILT 2026-10-25 (county pass, PR #171): governing body, row offices and District Attorney in every county, from the Blue Book rosters, each county's own website and the certified state abstracts (1,110 new files across seven commits, Baker as worked example plus six batches).</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5 items (2026-10-23).</t>
+          <t>13 items (2026-10-25): items 1, 2, 3 and 5 resolved by the county pass; items 6-13 are the county pass's own holds, conflicts and forward watches.</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Usually 3 or 5, by numbered positions</t>
+          <t>30 counties (3 or 5 seats)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The governing body in most of the 36 counties. County pass (fourth).</t>
+          <t>BUILT (PR #171, county pass 2026-10-25): numbered posts where the county's own listing gives positions or districts, one multi-seat post where it does not (Walter's rule, from his Baker/Jefferson checks). Separately elected Chairs in Clackamas, Hood River, Multnomah and Washington. Two seats sit vacant: Lincoln Position 2 and the Washington County Chair.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Eastern counties (factory: 6 -- Gilliam, Grant, Harney, Malheur, Sherman, Wheeler)</t>
+          <t>6 counties: Gilliam, Grant, Harney, Malheur, Sherman, Wheeler</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>OJD describes County Courts in SEVEN eastern counties -- Morrow is the divergence (Open Issues #1). The County Judge also carries judicial functions.</t>
+          <t>BUILT (PR #171, county pass 2026-10-25). The three-way divergence is resolved: the factory's six are exactly right -- Morrow is a Board of Commissioners on its own documents (Open Issues #1), and CROOK is also a Board of Commissioners on its own budget documents, superseding the Blue Book's County Court listing. Harney and Malheur judgeships were seated from the certified May 2022 County Judge contests in the state abstract; Gilliam's judge (Patnode, the former JP) was appointed in June 2024 after winning the primary.</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charters (9 counties) can combine, appoint, or replace offices (e.g. an elected County Auditor in 2 factory counties) -- per-county charter check.</t>
+          <t>BUILT (PR #171, county pass 2026-10-25). The charter counties vary the set sharply, verified county by county: Benton, Clatsop, Hood River, Lane, Multnomah, Umatilla and Washington each appoint or abolish several of these offices (Multnomah and Umatilla elect only the board, Sheriff, DA -- and Multnomah an Auditor). Assessor/Tax Collector is a combined elected office in Clackamas, Grant, Lake, Linn, Morrow, Union, Wasco and Yamhill; Josephine also elects a county Legal Counsel.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1 per county (conditional)</t>
+          <t>Elected in 19 counties</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Only where the county charter/ordinance has not made it appointed. Factory models 24.</t>
+          <t>BUILT where elected (PR #171): appointed in Benton, Clatsop, Columbia, Curry, Deschutes, Gilliam, Lincoln, Malheur, Sherman, Tillamook, Yamhill and others; not modeled where the county makes it appointive. One man, Michael Springer, is elected Surveyor of both Grant and Wheeler counties (modeled as one person, disclosed).</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Factory carries only 34 -- Clatsop and Hood River are factory gaps (Open Issues #2-3).</t>
+          <t>BUILT (PR #171, county pass 2026-10-25): every county's DA seated from the certified state abstracts -- the only county office the abstracts carry -- in two classes (21 counties elected 2024, 15 elected 2022) plus November specials in Columbia and Klamath (2024) and the Lincoln 2020 general precedent. The factory's Clatsop and Hood River gaps were factory errors (Open Issues #2-3, resolved). Mid-term turnovers built: Curry (Spansail -&gt; Kelley), Gilliam (Davis -&gt; Rodighiero; Davis is now Wasco's DA on the same person record). Jefferson's winner (Leriche) is contest-only -- his service is undocumented (Open Issues #8).</t>
         </is>
       </c>
     </row>
@@ -13550,12 +13550,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -13614,12 +13614,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -13646,12 +13646,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -13710,12 +13710,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -13774,12 +13774,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -13934,12 +13934,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -14030,12 +14030,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -14126,12 +14126,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -14190,12 +14190,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -14222,12 +14222,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -14350,12 +14350,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -14382,12 +14382,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -14414,12 +14414,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -14478,12 +14478,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -14510,12 +14510,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -14542,12 +14542,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -14574,12 +14574,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -14606,12 +14606,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -14638,12 +14638,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>None yet -- jurisdiction scaffold only</t>
+          <t>Governing body, elected row offices and District Attorney built 2026-10-25</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built -- county pass (PR #171)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -15681,7 +15681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15910,22 +15910,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Judicial pass, Justices of the Peace built on PR #171 (commit 2beb5a1), completing the judicial tier's build phase: 21 Justice Court organizations (on the existing county jurisdictions), 22 posts, 28 new people, 25 memberships, and 13 new county election files with 14 contests from county official results. Denominator from the SOS Blue Book county pages: 22 seats in 21 counties (Douglas has two districts) -- the factory's 20 seats missed Hood River and Union, and the Oregon Law Commission's '22 justice courts' agrees. The state abstracts carry no JP races and JP races are decided at the May primary on a majority (only Jackson and Union were November decisions). Three sitting JPs are gubernatorial appointees: Rastetter (Clackamas, effective 2026-01-01 on Brisbin's retirement -- factory right, Blue Book stale), Hayter (Gilliam, June 2024; the 2020 holder was Patnode), Joseph (Union, 2026-02-01). Union's 2022 winner Dall (7,938) carries a candidacy + contest but no membership -- his resignation date is undocumented, and the resulting winner-not-seated warning is the hold. Joe Charter's Nov 2024 JP win (43,176) was appended to his existing circuit-court person record (he left Circuit 1-8 in 2024). Blue Book term years overridden by county documents for Hood River (Harvey elected May 2022, Cascade Locks district), Klamath, Sherman and Tillamook (Connell re-elected May 2024; separate 2019-2024 membership from the county's 2018 order). Validation PASSED, 0 errors, 23 warnings (22 prior + the Dall hold). Remaining in the judicial pass: the circuit research items (17 seats).</t>
+          <t>County pass built on PR #171 (seven commits: Baker worked example dda1a83, then batches 9f4c7c0, 0d434c6, 99f9f91, 933e955, 2902471, 43c6104): governing body, elected row offices and District Attorney in all 36 counties -- 1,110 new files (orgs, posts, people, memberships, county election files carrying every DA contest from the certified state abstracts). Sources: SOS Blue Book county rosters (all 36 read firsthand), each county's own website for board structure and current holders, the OHA Commissioner and Judges Contact List (2025-06-04) as a cross-check, and the certified abstracts. Walter's rule applied: numbered commissioner posts where the county's own listing gives positions, one multi-seat post where it does not. County Courts are exactly the factory's six (Gilliam, Grant, Harney, Malheur, Sherman, Wheeler); Crook and Morrow are Boards of Commissioners on their own documents. Validation PASSED, 0 errors, 24 warnings (the 23 prior plus Jefferson's DA winner-not-seated hold, by design). County research items and forward watches are Open Issues #6-13.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Government Structure, Status Log, Open Issues</t>
+          <t>Government Structure, Counties, Status Log, Open Issues</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SOS Blue Book county pages (sos.oregon.gov); county clerks' certified results (Columbia, Douglas, Grant, Malheur, Tillamook, Clackamas, Deschutes, Hood River, Marion, Washington, Jackson, Union); Clackamas County releases and minutes (Rastetter appointment); Sherman County elected-officials list; Tillamook County BOC order (2018) and ACFRs</t>
+          <t>SOS Blue Book county pages; counties' own websites (board/elected-officials/budget documents, read 2026-10-25); OHA Commissioner and Judges Contact List 2025-06-04; SOS Abstracts of Votes 2022/2024 (Archives uris 13735452/13735456/13735458)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15942,20 +15942,47 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Judicial pass, Justices of the Peace built on PR #171 (commit 2beb5a1), completing the judicial tier's build phase: 21 Justice Court organizations (on the existing county jurisdictions), 22 posts, 28 new people, 25 memberships, and 13 new county election files with 14 contests from county official results. Denominator from the SOS Blue Book county pages: 22 seats in 21 counties (Douglas has two districts) -- the factory's 20 seats missed Hood River and Union, and the Oregon Law Commission's '22 justice courts' agrees. The state abstracts carry no JP races and JP races are decided at the May primary on a majority (only Jackson and Union were November decisions). Three sitting JPs are gubernatorial appointees: Rastetter (Clackamas, effective 2026-01-01 on Brisbin's retirement -- factory right, Blue Book stale), Hayter (Gilliam, June 2024; the 2020 holder was Patnode), Joseph (Union, 2026-02-01). Union's 2022 winner Dall (7,938) carries a candidacy + contest but no membership -- his resignation date is undocumented, and the resulting winner-not-seated warning is the hold. Joe Charter's Nov 2024 JP win (43,176) was appended to his existing circuit-court person record (he left Circuit 1-8 in 2024). Blue Book term years overridden by county documents for Hood River (Harvey elected May 2022, Cascade Locks district), Klamath, Sherman and Tillamook (Connell re-elected May 2024; separate 2019-2024 membership from the county's 2018 order). Validation PASSED, 0 errors, 23 warnings (22 prior + the Dall hold). Remaining in the judicial pass: the circuit research items (17 seats).</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Government Structure, Status Log, Open Issues</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SOS Blue Book county pages (sos.oregon.gov); county clerks' certified results (Columbia, Douglas, Grant, Malheur, Tillamook, Clackamas, Deschutes, Hood River, Marion, Washington, Jackson, Union); Clackamas County releases and minutes (Rastetter appointment); Sherman County elected-officials list; Tillamook County BOC order (2018) and ACFRs</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>Statewide executive completed on PR #171: Secretary of State (Read), State Treasurer (Steiner), and Attorney General (Rayfield) built from the certified Nov 5, 2024 abstract, and Commissioner of Labor and Industries (Stephenson) from the certified Nov 8, 2022 abstract -- each as org + post + new person + membership + election contest, cross-checked against the CivicMirror API's 2026 races. All 5 elected statewide offices now built. Validation on the OR tree PASSED, 0 errors. Also: the SOS retired the old sos.oregon.gov abstract PDF paths; abstracts are now published via the Oregon State Archives records system (records.sos.state.or.us), and the Governor-step source URLs were repaired to the current official location.</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Government Structure, Status Log</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>SOS Abstracts of Votes 2024 (Archives uri 13735458) and 2022 (uri 13735454); Multnomah County elected-officials page; BOLI commissioner page; CivicMirror API</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>
@@ -15972,7 +15999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16015,22 +16042,22 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Divergence (factory vs official)</t>
+          <t>Divergence (factory vs official) -- RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Morrow County governing body</t>
+          <t>Morrow (and Crook) County governing body</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Creyton's factory models Morrow as a 3-member Board of County Commissioners with no County Judge; the Oregon Judicial Department describes County Courts (County Judge + 2 commissioners) in SEVEN eastern counties, and the factory shows County Judge in only six (Gilliam, Grant, Harney, Malheur, Sherman, Wheeler). One of the two is wrong for Morrow.</t>
+          <t>Resolved at the county pass: Morrow's own documents (a 2024 plan signature block printing 'Commissioner, Chair, Position 3') establish a Board of Commissioners -- the factory was right and the OJD's seven-county County Court description is wrong for Morrow. The same check resolved CROOK the other way against the Blue Book: Crook's own budget documents a Board of Commissioners of three numbered positions, superseding the Blue Book's 'County Court / Judge Crawford' listing. County Courts are exactly six: Gilliam, Grant, Harney, Malheur, Sherman, Wheeler.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Morrow County charter / official county site, checked at the county pass; flag the loser on #170.</t>
+          <t>Done. Both counties built as Boards of Commissioners on PR #171.</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16067,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Factory gap</t>
+          <t>Factory gap -- RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -16050,12 +16077,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The factory carries no District Attorney office for Clatsop County. ORS 8.610 provides for a district attorney elected in each county, so this reads as a factory gap, not law.</t>
+          <t>Factory gap confirmed: Clatsop elects a DA (Ron Brown, certified May 2022 primary, 6,745). Built on PR #171. Clatsop's charter in fact elects only the Board (5 districts), Sheriff and DA -- Assessor, Clerk and Surveyor are appointed and the Treasurer's office was abolished.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Official SOS / county source at the county pass; mint from the official source and note the factory gap on #170.</t>
+          <t>Done.</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16092,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Factory gap</t>
+          <t>Factory gap -- RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -16075,12 +16102,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Same gap as Clatsop: no DA office in the factory for Hood River County, against ORS 8.610.</t>
+          <t>Factory gap confirmed: Hood River elects a DA (Matthew Ellis, certified May 2024 primary, 4,660 -- he had been Wasco County's DA in 2020). Built on PR #171.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Official SOS / county source at the county pass.</t>
+          <t>Done.</t>
         </is>
       </c>
     </row>
@@ -16115,22 +16142,222 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>Verification owed -- RESOLVED 2026-10-25</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>County officer sets, home-rule charter counties</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Every county's elected set was verified against its own website and charter documents at the county pass and built accordingly (PR #171). The thinnest sets: Multnomah and Umatilla (board, Sheriff, DA -- Multnomah also Auditor); the widest add an elected Auditor (Multnomah, Washington) or a Legal Counsel (Josephine).</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Source conflict -- clerk confirmation</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Baker County Commissioner Position 1 (Kaseberg)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>The county's own commissioners page shows Kaseberg's term as Jan. 2024-Dec. 2027; the Blue Book and the factory both give 2029. Modeled on the Blue Book class (from Jan. 2025) with the conflict quoted in her records.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Baker County Clerk confirmation; amend the record if the county's Jan. 2024 start (appointment, then election to the remainder) is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Source conflict -- clerk confirmation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Klamath County (Schutt term class; Nichols expiry)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>DA Schutt won at the November 2024 general after Costello's mid-term departure, but the Blue Book gives him a full term to 2029 although Klamath sits in the 2022 class. Separately, one county document gives Commissioner Nichols's expiry as January 2028 against the Blue Book's 2029. Both are modeled on the Blue Book with the conflicts disclosed.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Klamath County Clerk confirmation of the 2024 DA election's term and of Nichols's class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Research item</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Jefferson County District Attorney</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Leriche won the certified May 2024 primary (3,467), but a June 2025 Board agenda carries DA applicant presentations -- a vacancy being filled by appointment. Whether Leriche ever served, and who holds the office now, is undocumented in the sources read. Contest + candidacy only (the pass's one new winner-not-seated warning).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Jefferson County sources / clerk: Leriche's service and the appointed successor's identity and date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Forward watch -- November 3, 2026 election</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Lincoln County Commissioner Position 2; Washington County Chair</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Lincoln Position 2 is vacant (Hall departed) and is on the ballot as a two-year unexpired term. The Washington County Chair is vacant (Harrington resigned effective October 2, 2026); the successor elected November 3, 2026 is sworn in January 3, 2027.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Seat both winners from the certified November 2026 results after the election.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Forward watch -- November 3, 2026 election</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Deschutes County Board expansion and districting</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Measure 9-173 (approved Nov. 2024) adds Positions 4 and 5, elected at-large in November 2026 for initial two-year terms from January 2027. Measure 9-185 on the same ballot would switch the Board to five geographic districts (Map C) from the 2028 election. The Sheriff's office is also on the November 2026 ballot (Rupert's interim runs through December 31, 2026).</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Seat the Position 4/5 and Sheriff winners after certification; if 9-185 passes, plan the 2028 district restructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Forward watch -- January 2027</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Morrow County District Attorney</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>An October 2026 county meeting report says DA Nelson expects to leave for a circuit-court judgeship (District 6) in early January 2027.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify in January 2027; if he goes, end his DA membership, model the successor, and check the District 6 circuit vacancy against the circuit research queue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>Verification owed</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>County officer sets, 9 home-rule charter counties</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ORS 204.005's elected set (Sheriff / Clerk / Assessor / Treasurer / Commissioners) is varied by the 9 home-rule charters -- offices combined, appointed, or replaced (the factory shows an elected County Auditor in 2 counties and no Clerk/Assessor/Treasurer in several). No county's set is verified yet.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Each county's charter, read at the county pass before that county is built.</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Harney County Judge; Wallowa County third seat</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>An October 21, 2026 report outside county sources says Harney County Judge Hart resigned; unverified, and he is modeled as holding. Wallowa's third seat: Commissioner Roberts died in office July 30, 2025 (ended membership built); her successor is reported in meeting coverage as Cody Lathrop but is not verified on a county page.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>County sources for both; amend on documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Research items (county successions)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Josephine, Curry, Lane succession details</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Josephine's Martin and Richardson were appointed in January 2026 to vacant seats (dates/manner from county sources are summary-grade); Curry's Coker filled Alcorn's seat on an undocumented date and manner; Lane's elected Sheriff Harrold resigned in 2025 on an undocumented date (successor Wilkerson is built as appointed).</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>County minutes/orders for the exact instruments and dates; amend the records when documented.</t>
         </is>
       </c>
     </row>

--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Structure determined 2026-10-23 (issue #170 first pass). Federal tier built; statewide executive and legislative tiers built (PR #171); judicial, county, municipal, then schools / ESDs / special districts pending in Walter's order.</t>
+          <t>Structure determined 2026-10-23 (issue #170 first pass). Federal, statewide executive, legislative, judicial and county tiers built (PR #171); municipal tier BUILT 2026-10-25; schools / ESDs / special districts remain last in Walter's order.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>240 cities -- jurisdiction scaffolds only; municipal pass runs fifth (alphabetical batches of 10), factory as lead layer.</t>
+          <t>240 cities -- MUNICIPAL PASS COMPLETE 2026-10-25 (PR #171, 24 alphabetical batches of 10 plus a one-city catch-up batch 25): 218 built (orgs, posts, holders; 10 of them structure-only fail-closed), 22 HELD where no readable official roster exists. 3,534 new files: 218 organizations, 777 posts, 1,263 people, 1,265 memberships, 11 election files with 29 contests. Lakeside was missed at the batch 12/13 boundary (batch 13 was assembled partly from the factory city list, whose phantom 'Marion' entry took the slot; Marion is not one of the repo's 240 cities) and was caught by this workbook's per-city cross-check of jurisdiction files against built orgs, then built as batch 25 from the Coos County Clerk's certified November 2024 results.</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13 items (2026-10-25): items 1, 2, 3 and 5 resolved by the county pass; items 6-13 are the county pass's own holds, conflicts and forward watches.</t>
+          <t>19 items (2026-10-25): items 1, 2, 3 and 5 resolved by the county pass; items 6-13 are the county pass's holds, conflicts and forward watches; items 14-19 are the municipal pass's held cities, fail-closed builds, research queue, one scope question, the November 2026 forward watch, and the municipal factory concordance.</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Every Oregon city is a home-rule charter city -- mayor/council set, titles, and terms come from each city charter. Municipal pass (fifth), alphabetical batches of 10, factory as lead layer.</t>
+          <t>BUILT (PR #171, municipal pass 2026-10-25): every Oregon city is a home-rule charter city -- mayor/council set, titles, and terms come from each city's own documents. 218 cities built (218 organizations as the cities print them, 777 posts, 1,263 people, 1,265 memberships, 11 election files with 29 contests where certified figures were read firsthand); 22 cities HELD where no readable official roster exists (Open Issues #14); 10 built structure-only, fail-closed (Open Issues #15). Walter's post rule applied city by city: numbered posts where the city's own print gives positions, one multi-seat post where it does not. Thirteen cities have no separately elected mayor -- the council selects one from its membership (Baker City, Detroit, Durham, King City, Lowell, Maywood Park, Millersburg, Nyssa, Rivergrove, Sisters, Summerville, Sweet Home, Wood Village) -- and those mayors carry a single membership on the Mayor post. Three mayors currently hold by appointment to an elective office (Turner, Westfir, Tigard) and two seats sat vacant at build time (North Plains and Condon mayoralties). The factory's municipal layer misfiled TEN county rosters under city names, invented seat labels cities do not print, and carried phantom or departed names as incumbents -- every divergence was resolved against the city's own sources and is logged in Open Issues #19.</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1925,12 +1925,12 @@
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1973,12 +1973,12 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2021,12 +2021,12 @@
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2069,12 +2069,12 @@
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2117,12 +2117,12 @@
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -2165,12 +2165,12 @@
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2213,12 +2213,12 @@
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Positions 1/3/5 built unfilled: their holders are known as a set (Swope, Rayburn, Davidson) but not which holds which position.</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2309,12 +2309,12 @@
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -2357,12 +2357,12 @@
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -2405,12 +2405,12 @@
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -2453,12 +2453,12 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -2549,12 +2549,12 @@
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2597,12 +2597,12 @@
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -2645,12 +2645,12 @@
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2693,12 +2693,12 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2741,12 +2741,12 @@
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2789,12 +2789,12 @@
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2837,12 +2837,12 @@
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Sixth councilor seat unfilled: the reported 2026 appointment is unconfirmed in city documents.</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2885,12 +2885,12 @@
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2933,12 +2933,12 @@
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2981,12 +2981,12 @@
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3029,12 +3029,12 @@
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -3077,12 +3077,12 @@
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor built; the six councilor seats are built unfilled (the January 2024 roster is recorded in the repo org note).</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3125,12 +3125,12 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3173,12 +3173,12 @@
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3221,12 +3221,12 @@
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3269,12 +3269,12 @@
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3317,12 +3317,12 @@
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3365,12 +3365,12 @@
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3413,12 +3413,12 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3461,12 +3461,12 @@
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3509,12 +3509,12 @@
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -3557,12 +3557,12 @@
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3605,12 +3605,12 @@
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -3653,12 +3653,12 @@
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -3701,12 +3701,12 @@
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -3749,12 +3749,12 @@
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -3797,12 +3797,12 @@
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Three of six councilor seats seated; two reported holders rest on no readable city source and are not minted.</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -3845,12 +3845,12 @@
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -3893,12 +3893,12 @@
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -3941,12 +3941,12 @@
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -3989,12 +3989,12 @@
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4037,12 +4037,12 @@
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4085,12 +4085,12 @@
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Positions 1/2/6 built unfilled: Beck, Middleton and Woods hold them in unknown order.</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4133,12 +4133,12 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4181,12 +4181,12 @@
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -4229,12 +4229,12 @@
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor and Position 5 built from the Grant County Clerk's certified November 2024 abstract; Positions 1-4 built unfilled (Position 1 drew no filed candidate and 22 unnamed write-in votes).</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -4277,12 +4277,12 @@
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -4325,12 +4325,12 @@
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -4373,12 +4373,12 @@
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -4421,12 +4421,12 @@
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -4469,12 +4469,12 @@
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -4517,12 +4517,12 @@
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -4565,12 +4565,12 @@
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -4613,12 +4613,12 @@
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -4661,12 +4661,12 @@
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -4709,12 +4709,12 @@
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -4757,12 +4757,12 @@
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -4805,12 +4805,12 @@
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -4853,12 +4853,12 @@
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -4901,12 +4901,12 @@
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -4949,12 +4949,12 @@
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4997,12 +4997,12 @@
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -5045,12 +5045,12 @@
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -5093,12 +5093,12 @@
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -5141,12 +5141,12 @@
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -5189,12 +5189,12 @@
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -5237,12 +5237,12 @@
       <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -5285,12 +5285,12 @@
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Position 2 built unfilled: the factory's holder appears in no city document.</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -5333,12 +5333,12 @@
       <c r="H73" s="5" t="inlineStr"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Two of five councilor seats built unfilled: their reported holders rest on news + factory only.</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -5381,12 +5381,12 @@
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -5429,12 +5429,12 @@
       <c r="H75" s="5" t="inlineStr"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -5477,12 +5477,12 @@
       <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -5525,12 +5525,12 @@
       <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -5573,12 +5573,12 @@
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -5621,12 +5621,12 @@
       <c r="H79" s="5" t="inlineStr"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -5669,12 +5669,12 @@
       <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -5717,12 +5717,12 @@
       <c r="H81" s="5" t="inlineStr"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -5765,12 +5765,12 @@
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -5813,12 +5813,12 @@
       <c r="H83" s="5" t="inlineStr"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -5861,12 +5861,12 @@
       <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -5909,12 +5909,12 @@
       <c r="H85" s="5" t="inlineStr"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5957,12 +5957,12 @@
       <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -6005,12 +6005,12 @@
       <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -6053,12 +6053,12 @@
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -6101,12 +6101,12 @@
       <c r="H89" s="5" t="inlineStr"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor and Positions 4-6 built from Umatilla County's certified 2022 summary; Positions 1-3 built unfilled (Position 1's existence itself is unresolved).</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -6149,12 +6149,12 @@
       <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -6197,12 +6197,12 @@
       <c r="H91" s="5" t="inlineStr"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -6245,12 +6245,12 @@
       <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -6293,12 +6293,12 @@
       <c r="H93" s="5" t="inlineStr"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -6341,12 +6341,12 @@
       <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -6389,12 +6389,12 @@
       <c r="H95" s="5" t="inlineStr"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -6437,12 +6437,12 @@
       <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -6485,12 +6485,12 @@
       <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. No Mayor post built: no city source names a mayor (the council is led by its President) -- research item. Fifth councilor seat unfilled.</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -6533,12 +6533,12 @@
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -6581,12 +6581,12 @@
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -6629,12 +6629,12 @@
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -6677,12 +6677,12 @@
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -6725,12 +6725,12 @@
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -6773,12 +6773,12 @@
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6821,12 +6821,12 @@
       <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Two councilor seats unfilled after July 2025 resignations recorded in the city's FY2024-25 audit.</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -6869,12 +6869,12 @@
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -6917,12 +6917,12 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -6965,12 +6965,12 @@
       <c r="H107" s="5" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -7013,12 +7013,12 @@
       <c r="H108" s="5" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -7061,12 +7061,12 @@
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Sixth councilor seat unfilled; it is on the November 2026 ballot as a two-year unexpired term.</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -7109,12 +7109,12 @@
       <c r="H110" s="5" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -7157,12 +7157,12 @@
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -7205,12 +7205,12 @@
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -7253,12 +7253,12 @@
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -7301,12 +7301,12 @@
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -7349,12 +7349,12 @@
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -7397,12 +7397,12 @@
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -7445,12 +7445,12 @@
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -7493,12 +7493,12 @@
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Partial after a spring 2026 mass resignation: only the appointed mayor and one continuing councilor are minted; the rest are disclosed in the repo org note.</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -7541,12 +7541,12 @@
       <c r="H119" s="5" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -7589,12 +7589,12 @@
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Position 3 built unfilled (printed 'Vacant' in the city's October 2025 resolution signature block).</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -7637,12 +7637,12 @@
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -7685,12 +7685,12 @@
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor built from the Blue Book; the three councilor seats are unfilled (factory names not minted).</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -7733,12 +7733,12 @@
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor built; Positions 1-4 unfilled -- the factory names rest on a Grant County certified abstract not read in this pass.</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -7781,12 +7781,12 @@
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -7829,12 +7829,12 @@
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -7877,12 +7877,12 @@
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -7925,12 +7925,12 @@
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Two of six councilor seats vacant after the April and August 2026 resignations of Yoder and Seibold; temporary appointments were authorized but their seating is unconfirmed.</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -7973,12 +7973,12 @@
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. Roster page does not extract as text; structure corroborated by the Klamath County November 2026 sample ballot. Factory names disclosed in the repo org note only. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -8021,12 +8021,12 @@
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -8069,12 +8069,12 @@
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -8117,12 +8117,12 @@
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -8165,12 +8165,12 @@
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -8213,12 +8213,12 @@
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -8261,12 +8261,12 @@
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor post built unfilled: no city document read names a mayor. Councilors seated with factory-grade first names, flagged (the Brownsville pattern).</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -8309,12 +8309,12 @@
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. City homepage states a mayor and six council positions (two vacant) but names nobody; the factory's seven names conflict with the vacancy statement. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -8357,12 +8357,12 @@
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. The city site publishes no current roster (indexed minutes are 2018-2020). Factory names disclosed in the repo org note only. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -8405,12 +8405,12 @@
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -8453,12 +8453,12 @@
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -8501,12 +8501,12 @@
       <c r="H139" s="5" t="inlineStr"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -8549,12 +8549,12 @@
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -8597,12 +8597,12 @@
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -8645,12 +8645,12 @@
       <c r="H142" s="5" t="inlineStr"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. No readable roster on the city site. Factory names disclosed in the repo org note only. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -8693,12 +8693,12 @@
       <c r="H143" s="5" t="inlineStr"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -8741,12 +8741,12 @@
       <c r="H144" s="5" t="inlineStr"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor built from the Blue Book; Positions 1-6 unfilled -- the 2024 write-in winners are unnamed in every official source read.</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -8789,12 +8789,12 @@
       <c r="H145" s="5" t="inlineStr"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -8837,12 +8837,12 @@
       <c r="H146" s="5" t="inlineStr"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -8885,12 +8885,12 @@
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. The city site could not be read in this pass (resolver failure). Factory names disclosed in the repo org note only. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -8933,12 +8933,12 @@
       <c r="H148" s="5" t="inlineStr"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
@@ -8981,12 +8981,12 @@
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -9029,12 +9029,12 @@
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Three of six councilor seats seated from the newest roster-bearing city document (c. June 2024); the other class's replacements are not documented.</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -9077,12 +9077,12 @@
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Position 2 built unfilled: the November 2024 winner vacated; the unexpired term is on the November 3, 2026 ballot.</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -9125,12 +9125,12 @@
       <c r="H152" s="5" t="inlineStr"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -9173,12 +9173,12 @@
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
@@ -9221,12 +9221,12 @@
       <c r="H154" s="5" t="inlineStr"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -9269,12 +9269,12 @@
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -9317,12 +9317,12 @@
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -9365,12 +9365,12 @@
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
@@ -9413,12 +9413,12 @@
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
@@ -9461,12 +9461,12 @@
       <c r="H159" s="5" t="inlineStr"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Sixth councilor seat unfilled: the factory's holder is unconfirmable in any official source.</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -9509,12 +9509,12 @@
       <c r="H160" s="5" t="inlineStr"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
@@ -9557,12 +9557,12 @@
       <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
@@ -9605,12 +9605,12 @@
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -9653,12 +9653,12 @@
       <c r="H163" s="5" t="inlineStr"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -9701,12 +9701,12 @@
       <c r="H164" s="5" t="inlineStr"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -9749,12 +9749,12 @@
       <c r="H165" s="5" t="inlineStr"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -9797,12 +9797,12 @@
       <c r="H166" s="5" t="inlineStr"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Three of six councilor seats seated; three factory names are unconfirmed in any current city source and are not minted.</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -9845,12 +9845,12 @@
       <c r="H167" s="5" t="inlineStr"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -9893,12 +9893,12 @@
       <c r="H168" s="5" t="inlineStr"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -9941,12 +9941,12 @@
       <c r="H169" s="5" t="inlineStr"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. No readable official roster exists (the factory's URL 404s). Factory names disclosed in the repo org note only. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -9989,12 +9989,12 @@
       <c r="H170" s="5" t="inlineStr"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -10037,12 +10037,12 @@
       <c r="H171" s="5" t="inlineStr"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. The Blue Book Prescott page would not render; Blue Book city pages carry no councilor roster in any case. Factory names disclosed in the repo org note only; Columbia County Clerk certified results are the verification route. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -10085,12 +10085,12 @@
       <c r="H172" s="5" t="inlineStr"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -10133,12 +10133,12 @@
       <c r="H173" s="5" t="inlineStr"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -10181,12 +10181,12 @@
       <c r="H174" s="5" t="inlineStr"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -10229,12 +10229,12 @@
       <c r="H175" s="5" t="inlineStr"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -10277,12 +10277,12 @@
       <c r="H176" s="5" t="inlineStr"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -10325,12 +10325,12 @@
       <c r="H177" s="5" t="inlineStr"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -10373,12 +10373,12 @@
       <c r="H178" s="5" t="inlineStr"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -10421,12 +10421,12 @@
       <c r="H179" s="5" t="inlineStr"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -10469,12 +10469,12 @@
       <c r="H180" s="5" t="inlineStr"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -10517,12 +10517,12 @@
       <c r="H181" s="5" t="inlineStr"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -10565,12 +10565,12 @@
       <c r="H182" s="5" t="inlineStr"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -10613,12 +10613,12 @@
       <c r="H183" s="5" t="inlineStr"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -10661,12 +10661,12 @@
       <c r="H184" s="5" t="inlineStr"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -10709,12 +10709,12 @@
       <c r="H185" s="5" t="inlineStr"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -10757,12 +10757,12 @@
       <c r="H186" s="5" t="inlineStr"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. Structure verified on the city council page, but the city publishes no readable roster. Factory names disclosed in the repo org note only. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -10805,12 +10805,12 @@
       <c r="H187" s="5" t="inlineStr"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -10853,12 +10853,12 @@
       <c r="H188" s="5" t="inlineStr"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -10901,12 +10901,12 @@
       <c r="H189" s="5" t="inlineStr"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -10949,12 +10949,12 @@
       <c r="H190" s="5" t="inlineStr"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -10997,12 +10997,12 @@
       <c r="H191" s="5" t="inlineStr"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -11045,12 +11045,12 @@
       <c r="H192" s="5" t="inlineStr"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -11093,12 +11093,12 @@
       <c r="H193" s="5" t="inlineStr"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -11141,12 +11141,12 @@
       <c r="H194" s="5" t="inlineStr"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Position 2 vacant (a two-year unexpired term is on the November 2026 ballot); Position 3 unfilled -- its factory name rests on the factory lead alone.</t>
         </is>
       </c>
     </row>
@@ -11178,7 +11178,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -11189,12 +11189,12 @@
       <c r="H195" s="5" t="inlineStr"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -11237,12 +11237,12 @@
       <c r="H196" s="5" t="inlineStr"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -11285,12 +11285,12 @@
       <c r="H197" s="5" t="inlineStr"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Fifth seat unfilled: the last city-confirmed holder (2023) and the factory's name cannot be reconciled; the city site is stale (documents run 2021-2023), so the whole roster's currency past 2023 is a research item.</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -11333,12 +11333,12 @@
       <c r="H198" s="5" t="inlineStr"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -11381,12 +11381,12 @@
       <c r="H199" s="5" t="inlineStr"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -11429,12 +11429,12 @@
       <c r="H200" s="5" t="inlineStr"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -11477,12 +11477,12 @@
       <c r="H201" s="5" t="inlineStr"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -11525,12 +11525,12 @@
       <c r="H202" s="5" t="inlineStr"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -11573,12 +11573,12 @@
       <c r="H203" s="5" t="inlineStr"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -11621,12 +11621,12 @@
       <c r="H204" s="5" t="inlineStr"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -11669,12 +11669,12 @@
       <c r="H205" s="5" t="inlineStr"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -11717,12 +11717,12 @@
       <c r="H206" s="5" t="inlineStr"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -11765,12 +11765,12 @@
       <c r="H207" s="5" t="inlineStr"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -11813,12 +11813,12 @@
       <c r="H208" s="5" t="inlineStr"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -11861,12 +11861,12 @@
       <c r="H209" s="5" t="inlineStr"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Mayor built; all six councilor memberships HELD -- three traces agree on the set, but two spellings (Collay/Cooley; Ana/Anna Byers) are unresolved on any printed city document. Names disclosed in the repo org note.</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -11909,12 +11909,12 @@
       <c r="H210" s="5" t="inlineStr"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -11957,12 +11957,12 @@
       <c r="H211" s="5" t="inlineStr"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
@@ -12005,12 +12005,12 @@
       <c r="H212" s="5" t="inlineStr"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -12053,12 +12053,12 @@
       <c r="H213" s="5" t="inlineStr"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -12101,12 +12101,12 @@
       <c r="H214" s="5" t="inlineStr"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -12149,12 +12149,12 @@
       <c r="H215" s="5" t="inlineStr"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Three of six councilor seats unfilled: their reported holders rest on non-official meeting transcripts only.</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -12197,12 +12197,12 @@
       <c r="H216" s="5" t="inlineStr"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -12245,12 +12245,12 @@
       <c r="H217" s="5" t="inlineStr"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -12293,12 +12293,12 @@
       <c r="H218" s="5" t="inlineStr"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -12341,12 +12341,12 @@
       <c r="H219" s="5" t="inlineStr"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -12389,12 +12389,12 @@
       <c r="H220" s="5" t="inlineStr"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -12437,12 +12437,12 @@
       <c r="H221" s="5" t="inlineStr"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -12485,12 +12485,12 @@
       <c r="H222" s="5" t="inlineStr"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -12533,12 +12533,12 @@
       <c r="H223" s="5" t="inlineStr"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -12581,12 +12581,12 @@
       <c r="H224" s="5" t="inlineStr"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Two of four councilor seats unfilled: their reported holders rest on the factory lead plus newspaper meeting reports only.</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -12629,12 +12629,12 @@
       <c r="H225" s="5" t="inlineStr"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. One councilor seat vacant: Booth resigned September 10, 2026; no successor appointment appears in city records; the seat is on the November 3, 2026 ballot.</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -12677,12 +12677,12 @@
       <c r="H226" s="5" t="inlineStr"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -12725,12 +12725,12 @@
       <c r="H227" s="5" t="inlineStr"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -12773,12 +12773,12 @@
       <c r="H228" s="5" t="inlineStr"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -12821,12 +12821,12 @@
       <c r="H229" s="5" t="inlineStr"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -12869,12 +12869,12 @@
       <c r="H230" s="5" t="inlineStr"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -12917,12 +12917,12 @@
       <c r="H231" s="5" t="inlineStr"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -12965,12 +12965,12 @@
       <c r="H232" s="5" t="inlineStr"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>HELD -- no readable official roster</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: nothing built. No official city website, published roster, or county certified record naming this city's officers could be read; the factory lead alone is never a minting source. Route: county clerk certified results or a city records request (Open Issues #14).</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -13013,12 +13013,12 @@
       <c r="H233" s="5" t="inlineStr"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. The city council page verifies the structure (mayor + five councilors, four-year terms, read firsthand) but prints no member names. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -13061,12 +13061,12 @@
       <c r="H234" s="5" t="inlineStr"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -13109,12 +13109,12 @@
       <c r="H235" s="5" t="inlineStr"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -13157,12 +13157,12 @@
       <c r="H236" s="5" t="inlineStr"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -13205,12 +13205,12 @@
       <c r="H237" s="5" t="inlineStr"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Position 2 carries no membership: its holder, Rios-Campos, was selected by the council as Mayor and his single membership sits on the Mayor post.</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -13253,12 +13253,12 @@
       <c r="H238" s="5" t="inlineStr"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (partial) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25. Ward 1 vacant (city vacancy notice; the appointee will serve the remainder of the term expiring December 2028). The departed holder's exit is undocumented and he is not modeled.</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -13301,12 +13301,12 @@
       <c r="H239" s="5" t="inlineStr"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -13349,12 +13349,12 @@
       <c r="H240" s="5" t="inlineStr"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: governing body built from the city's own published roster, charter, minutes or budget documents (batch verification notes in the repo org record); election records filed only where certified figures were read firsthand.</t>
         </is>
       </c>
     </row>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>Home-rule charter -- link to verify at municipal pass</t>
+          <t>Home-rule charter -- per-city form verified at municipal pass</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -13397,12 +13397,12 @@
       <c r="H241" s="5" t="inlineStr"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>Scaffold only</t>
+          <t>Built (structure only) -- municipal pass (PR #171)</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>Census 2022-seeded jurisdiction scaffold; no posts built yet. Municipal pass: alphabetical batches of 10, factory v0.1 as lead layer.</t>
+          <t>Municipal pass 2026-10-25: organization and posts built fail-closed with NO memberships. Certified 2024 winners (Wertz, Wertz, Grabinski) cannot be reconciled with a December 23, 2025 federal court opinion naming Paulene Kingery as Mayor after undocumented 2025 resignations. Disclosed in full in the repo org note. (Open Issues #15.)</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15988,6 +15988,33 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Municipal pass COMPLETE on PR #171 (24 alphabetical batches of 10 cities plus a one-city catch-up batch, 21 commits from 2d63fba through 45750a1): all 240 cities accounted for -- 218 built, 22 HELD (Open Issues #14). 3,534 new files: 218 organizations (named as each city prints its body), 777 posts, 1,263 people, 1,265 memberships, and 11 election files with 29 contests where certified figures were read firsthand (Adair Village, Antelope, Dayville, Gold Hill, Gresham, Helix, Hermiston, Lakeside, Reedsport, Riddle, Summerville). Lakeside was missed at the batch 12/13 boundary -- batch 13's list came partly from the factory, whose phantom 'Marion' entry (the misfiled Marion County roster; Marion is not one of the repo's 240 cities) took the slot -- and was caught by this workbook's cross-check of jurisdiction files against built orgs; it was then built as batch 25 entirely from the Coos County Clerk's certified November 5, 2024 totals report and the city's candidate certification, both read firsthand, which also resolved that Councilor Nikki Harden is a distinct person from Mayor Nikki Wood. Method: the factory's municipal layer as lead only; a per-batch verification sweep of each city's own site, charter, minutes and budget documents; at least one decisive claim spot-checked firsthand per batch; Walter's post rule (numbered posts where the city's own print gives positions, one multi-seat post where it does not). Ten cities are built structure-only, fail-closed (Open Issues #15); roughly thirty more carry an unfilled seat or an unminted name, each disclosed in its repo org note and on the Municipalities sheet. Thirteen cities choose their mayor from the council (single membership on the Mayor post); three mayors hold an elective office by appointment (Tigard, Turner, Westfir); two mayoralties sat vacant (North Plains, Condon). Validation on the OR tree PASSED after every batch, 0 errors, with the warning count never rising above the 24-warning baseline. The factory's municipal layer misfiled TEN county rosters under city names and repeatedly invented seat labels and incumbents (Open Issues #19).</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Municipalities, Government Structure, README, Status Log, Open Issues</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Each city's own website, charter, minutes, budget and elections documents (per-batch verification files); county clerks' certified results (Grant, Umatilla, Douglas, Lincoln, Marion, Union, Sherman, Columbia); SOS Blue Book city pages (Lonerock, Monument mayors); City of Warrenton Official Statement (EMMA/MSRB)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15999,7 +16026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16361,6 +16388,156 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>HELD cities -- no readable official roster</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>22 cities: Adrian, Burns, Depoe Bay, Dunes City, Gervais, Granite, Hines, Johnson City, Jordan Valley, Lostine, Mitchell, Richland, Rufus, Seneca, Spray, St. Paul, Ukiah, Unity, Wallowa, Wasco, Waterloo, Weston</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Nothing is built for these cities: no official city website, published roster, or county certified record naming their officers could be read in the municipal pass, and the factory lead alone is never a minting source. Burns is the sharpest case: the factory's five-seat roster conflicts with the city's own January 2023 minutes showing at least six NUMBERED councilor seats, and no newer full roster exists. Two of the factory's entries in this set (Wallowa, Wasco) were county rosters misfiled under the city name, so even the factory's city-level lead is absent there. NOTE: 'Marion' is NOT one of the repo's 240 cities (Marion, Oregon is an unincorporated community; the factory's 'Marion' entry was the misfiled Marion County roster) -- it is not a held city. Lakeside WAS initially missed at the batch 12/13 boundary for the same reason and was caught by this workbook's cross-check and built as batch 25, so the final accounting is 218 built / 22 held / 240 total.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>County clerk certified results or city records requests, city by city (the VT/MA clerk pattern).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Fail-closed builds -- structure verified, memberships owed</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10 cities: Malin, Metolius, Mill City, Monmouth, Mount Angel, Powers, Prescott, Scio, Wheeler, Yoncalla</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Organization and posts are built with NO memberships: in each city the structure is verified from an official source but no readable roster names the current holders (details per city on the Municipalities sheet). Yoncalla is the special case: its certified 2024 winners cannot be reconciled with a December 2025 federal court opinion naming a different mayor after undocumented 2025 resignations, so nobody is seated until the city's own records or the county clerk's post-2025 filings resolve who holds office.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>A published roster, a clerk-certified roster, or a records request per city; Yoncalla needs the Douglas County Clerk's post-2025 filings or the city's own minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Research queue -- partial municipal builds</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>About 30 cities (see the Municipalities sheet notes)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Unfilled seats and unminted names left by the pass, each disclosed in its repo organization note: unmapped position assignments (Arlington 1/3/5, Culver 1/2/6, John Day pattern cases), unconfirmed appointments (Boardman, Madras's two seats, Prineville's reported Thrasher appointment sits in batch notes), unconfirmable factory names (Gaston Position 2, Oakridge's sixth seat, Helix Position 1's existence), transcript-grade holders (Troutdale's three seats, Vernonia's two), first-name gaps on the Brownsville pattern (Brownsville, Merrill, Scotts Mills' surnames, Stanfield's Haigh/Zielke classes), Talent's two unresolved spellings (Collay/Cooley; Ana/Anna Byers), Siletz Position 3, Sodaville's fifth seat and stale-roster currency, Idanha's mayor question, Gold Hill's Wright departure/Berggren seating instruments, Monroe's Felty expiry conflict, Molalla's mayoral term length, Nyssa's charter text, Oakland's Wier/Rochester currency past 2024, Rainier's Ratkie appointment and Kreger resignation reports, and Long Creek's unread Grant County abstract.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>City minutes, charters and clerk records per item; none blocks the pass. Talent resolves on any single printed city document naming its councilors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Scope question -- Walter's call</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Shaniko: elected City Recorder</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Shaniko elects a City Recorder (Krista Miller) alongside its council -- a non-council elected municipal office, recorded in the repo org note but NOT built. Whether recorder/treasurer-style elected city offices are in Civic-Data scope is undecided; other cities may have them (recorders are usually appointed).</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Walter's scope ruling; if IN, sweep the municipal tier for other elected non-council offices before building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Forward watch -- November 2026 / January 2027 municipal turnover</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Dozens of cities</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Large turnover lands January 2027: the November 3, 2026 ballot carries mayoralties and council classes across the state, the May 2026 primary already decided some seats (Hermiston's Van Veen and Martin take office January 1, 2027; Salem's and Springfield's 2026 classes likewise), and named vacancies are on the ballot or in appointment processes: Adair Village Ward 2, Nehalem Position 2, Siletz Position 2, Woodburn Ward 1 (appointee), the North Plains and Condon mayoralties, Gold Beach Position 5 (NO candidate filed), Rockaway Beach Position 3 (appointment applications due November 5, 2026), Lake Oswego's vacant seat, Junction City's unexpired seat, Rainier's mayoral succession (Cole moves to a Columbia County Commissioner seat in January 2027), Roseburg's mayoralty and four Position 1 seats, Shady Cove's mayoralty (two-year term from January 1, 2027), Tigard's mayoralty (Hu as incumbent), and Newport's mayoral race.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>After certification: seat the November 2026 winners, end the departed memberships, and fill the named vacancies; fold into the same post-election sweep as Open Issues #9-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Factory concordance -- municipal layer</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Creyton Loud OR Jurisdiction Factory v0.1 (municipal tabs)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>The factory's municipal layer, used as lead only, diverged from official sources at a rate the county layer did not: TEN county rosters misfiled under city names (Hood River, Jefferson, Marion, Tillamook, Umatilla, Union, Wallowa, Wasco, Wheeler, Yamhill); seat labels invented wholesale ('At-Large Slot N' in at least a dozen cities whose print has none); phantom or applicant names carried as incumbents (Toledo's Strom, Gladstone's Farley, Gaston's Holcomb, Irrigon's invented 'Martin Brown Jr.', Boardman's applicant Hughes); a mayor mis-seated as a councilor (Nyssa) and a councilor mis-seated as MAYOR (Riddle); councils understated (Riddle 5 vs 6 positions, Klamath Falls 4 wards vs 5, Sandy 5 vs 6, Harrisburg 5 vs 6, Lexington 3 vs 4, Grass Valley 3 vs 6); officeholders omitted entirely (Cornelius's Vaughn, Drain's Savage, Harrisburg's Thomas, Nyssa's Ramos, Turner's Taylor, Irrigon's Serratos/Bishop, Nehalem's Position 2); and scrape dates stamped as term boundaries (Newport's February 1 ends, Seaside's uniform 2027 ends, Seneca's single meeting date). Counterweights: batch 7 (Elkton..Garibaldi) checked out name-for-name, The Dalles and Tualatin matched exactly, and Waldport/Warrenton/Westfir rosters were confirmed. Full per-city detail is in the repo org notes and the pass's batch verification files.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Feedback for Creyton via Walter; no repo action. The pattern argues for treating the factory's municipal ROSTERS as unverified until a city source confirms them, while its STRUCTURE leads (charters, seat counts) were right more often than not.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reference/OR Rolling Audit/OR_Municipalities.xlsx
+++ b/reference/OR Rolling Audit/OR_Municipalities.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Government Structure" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Municipalities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="School Districts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Counties" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Office Titles (Ref)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Status Log" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Open Issues" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Government Structure" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Municipalities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="School Districts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counties" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Titles (Ref)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Issues" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19 items (2026-10-25): items 1, 2, 3 and 5 resolved by the county pass; items 6-13 are the county pass's holds, conflicts and forward watches; items 14-19 are the municipal pass's held cities, fail-closed builds, research queue, one scope question, the November 2026 forward watch, and the municipal factory concordance.</t>
+          <t>19 items (2026-10-25): items 1, 2, 3 and 5 resolved by the county pass; items 6-13 are the county pass's holds, conflicts and forward watches; items 14-19 are the municipal pass's held cities, fail-closed builds, research queue, one scope question, the November 2026 forward watch, and the municipal factory concordance. Research step 2026-10-25: items 6, 7, 12 and 13 resolved, item 8 partially resolved, item 11 upgraded to an announced appointment, and item 4's JP leftovers closed except seven clerk-request totals.</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>BUILT (PR #171, JP slice of the judicial pass, commit 2beb5a1): one Justice Court organization per county on the existing county jurisdictions, 22 posts, 28 new people, 25 memberships, 14 contests in 13 new county election files from county official results (the state abstracts carry no JP races). Denominator = SOS Blue Book county pages: 22 seats -- the factory's 20 missed Hood River and Union. Three holders are gubernatorial appointees (Rastetter/Clackamas 2026, Hayter/Gilliam 2024, Joseph/Union 2026); Union's 2022 winner Dall is held without a membership (resignation date undocumented -- the tier's one winner-not-seated warning). Blue Book term years were wrong for Hood River, Klamath, Sherman and Tillamook and were overridden by county documents, disclosed in the source notes. Certified totals not posted online for Baker, Harney, Wheeler, Klamath, Lane, Linn, Sherman and Gilliam-2020 are clerk-request items.</t>
+          <t>BUILT (PR #171, JP slice of the judicial pass, commit 2beb5a1): one Justice Court organization per county on the existing county jurisdictions, 22 posts, 28 new people, 25 memberships, 14 contests in 13 new county election files from county official results (the state abstracts carry no JP races). Denominator = SOS Blue Book county pages: 22 seats -- the factory's 20 missed Hood River and Union. Three holders are gubernatorial appointees (Rastetter/Clackamas 2026, Hayter/Gilliam 2024, Joseph/Union 2026); Union's 2022 winner Dall's elected membership was built in the research step 2026-10-25 (resigned effective February 1, 2026, when Joseph's appointment took effect); Gilliam's Patnode end is pinned to May 31, 2024 and Hayter's start to June 1, 2024; Linn's Meyer gained her appointed span from January 1, 2019; Hood River confirmed to have a single JP district. Blue Book term years were wrong for Hood River, Klamath, Sherman and Tillamook and were overridden by county documents, disclosed in the repo source notes. Klamath's certified total was found and filed (Oakes 10,374, May 2022); certified totals not posted online for Baker, Harney, Wheeler, Lane, Linn, Sherman and Gilliam-2020 remain clerk-request items.</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>BUILT (PR #171, county pass 2026-10-25): every county's DA seated from the certified state abstracts -- the only county office the abstracts carry -- in two classes (21 counties elected 2024, 15 elected 2022) plus November specials in Columbia and Klamath (2024) and the Lincoln 2020 general precedent. The factory's Clatsop and Hood River gaps were factory errors (Open Issues #2-3, resolved). Mid-term turnovers built: Curry (Spansail -&gt; Kelley), Gilliam (Davis -&gt; Rodighiero; Davis is now Wasco's DA on the same person record). Jefferson's winner (Leriche) is contest-only -- his service is undocumented (Open Issues #8).</t>
+          <t>BUILT (PR #171, county pass 2026-10-25): every county's DA seated from the certified state abstracts -- the only county office the abstracts carry -- in two classes (21 counties elected 2024, 15 elected 2022) plus November specials in Columbia and Klamath (2024) and the Lincoln 2020 general precedent. The factory's Clatsop and Hood River gaps were factory errors (Open Issues #2-3, resolved). Mid-term turnovers built: Curry (Spansail -&gt; Kelley), Gilliam (Davis -&gt; Rodighiero; Davis is now Wasco's DA on the same person record). Jefferson's winner Leriche is now built: an elected span ending with his February 2, 2025 resignation plus an open acting span (he was appointed acting DA; no permanent appointment documented -- Open Issues #8). Klamath's Schutt gained his appointed span from December 21, 2023 and Costello's elected membership was built (Open Issues #7, resolved).</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16010,6 +16010,33 @@
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>CivicMirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Research step built on PR #171 (commit 45fc75b): all five research sweeps resolved and built -- 97 files added, 23 removed (renames and the merged Summer duplicate), 14 edited in place; validation PASSED, 0 errors, warnings down from 24 to the 10-warning baseline (9 federal no-election-trace + the by-design HD34 hold). CIRCUIT: the abstract parser was vindicated on all four class contradictions (the directory holders were 2026 appointees); five new judgeships seated (May, Knight, Brown, Bartov, Whiteley); four departure-to-appointment seats completed both sides (Ryan/Dozono, Allen/Ridenour, Steele/Gilmartin, Kersey/Dougherty); three 2026 retirements ended with the seats vacant to the ballot (Waller, Holmes Hehn, Flint); 17 of the 18 cross-cycle successors had served by appointment first -- their appointed spans are built and the departed winners' ended memberships with them (exceptions: Bloch, Bunch and Holland won terms they never began -- no memberships, by design; Jacquot's circuit start is undocumented, her Court of Appeals appointed span is built instead; Erious Johnson Jr., the appointed incumbent who lost in 2022, is added as a person with membership and candidacy). 20-14: Miranda Summer and Maalik Summer are the same person -- records merged under the ballot name with the current name documented (a name-change fallback keeps validation clean). JP: Dall's membership built (resigned eff. 2026-02-01), Patnode/Hayter dates pinned, Meyer's 2019 appointed span added, Klamath's certified Oakes total found and filed (10,374); seven JP totals remain clerk-request items. COUNTY: Jefferson DA Leriche built (elected span + open acting span; permanent appointment undocumented, Nisley not seated); Klamath Schutt/Costello completed; Harney Hart ended 2026-10-21; Wallowa Hayward (appointed) + Lathrop (elected) built; Josephine starts corrected to 2026-02-18; Curry Coker corrected to appointed from 2025-05-02; Lane Wilkerson split into acting + appointed spans and Harrold built. Workbook Open Issues #6, #7, #12, #13 resolved; #8 partially; #11 upgraded (Nelson's District 6 appointment announced, effective January 1, 2027).</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Status Log, Open Issues, Government Structure</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Governor's Office newsroom releases (apps.oregon.gov) and the Oregon open-data newsroom archive (data.oregon.gov iqjz-cgey), read firsthand; SOS Abstracts of Votes 2020-2024; county clerks' certified statements (Klamath); county commissioners' pages and minutes (Wallowa, Curry, Josephine, Harney, Lane); Federal Judicial Center (Baggio)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>CivicMirror</t>
         </is>
@@ -16159,7 +16186,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Done. Leftovers in the research queue: certified totals not posted online for 8 seats (clerk requests), Dall's resignation date (Union), Joseph's appointment announcement, Charter's circuit departure date, and whether Hood River has a second justice district.</t>
+          <t>Done. Research step 2026-10-25 resolved the leftovers: Dall's elected membership is built (resigned effective February 1, 2026); Joseph's appointment is verified as the Governor's (announced January 15, 2026, effective February 1, 2026); Charter retired from Circuit 1-8 effective May 1, 2023; Hood River has NO second justice district (single JP, county Justice Court page + Blue Book + 2020 charter). Klamath's certified JP total was FOUND (Oakes 10,374, May 17, 2022; contest filed). Seven certified totals remain clerk-request items: Sherman Johnson 2020, Baker Kerns 2024, Harney Richardson 2024, Lane Brissenden 2022, Linn Meyer 2020, Gilliam Patnode 2020, Wheeler Ordway Campbell 2020.</t>
         </is>
       </c>
     </row>
@@ -16194,7 +16221,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Source conflict -- clerk confirmation</t>
+          <t>Source conflict -- RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -16204,12 +16231,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The county's own commissioners page shows Kaseberg's term as Jan. 2024-Dec. 2027; the Blue Book and the factory both give 2029. Modeled on the Blue Book class (from Jan. 2025) with the conflict quoted in her records.</t>
+          <t>The county's commissioners page showed Kaseberg's term as Jan. 2024-Dec. 2027 against the Blue Book's 2029 class. Research step resolution: she was NOT appointed in January 2024 -- Commissioner Nichols retired and the seat was filled at the November 5, 2024 general election, which she won. The county page's term line is wrong at BOTH ends (shifted exactly one year early). The modeled class (January 2025 - January 2029) stands; the resolution is sourced on her membership record.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Baker County Clerk confirmation; amend the record if the county's Jan. 2024 start (appointment, then election to the remainder) is confirmed.</t>
+          <t>Done.</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16246,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Source conflict -- clerk confirmation</t>
+          <t>Source conflict -- RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -16229,12 +16256,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>DA Schutt won at the November 2024 general after Costello's mid-term departure, but the Blue Book gives him a full term to 2029 although Klamath sits in the 2022 class. Separately, one county document gives Commissioner Nichols's expiry as January 2028 against the Blue Book's 2029. Both are modeled on the Blue Book with the conflicts disclosed.</t>
+          <t>Research step resolution: DA David A. Schutt was appointed by Governor Kotek on December 21, 2023 after Eve Costello resigned (Costello's elected membership is now built, ending December 2023 at month precision); Schutt then won the November 5, 2024 general (18,730) for a FULL term to January 2029, per the County Clerk's elected-positions sheet (next DA election May 2028) -- his appointed span (2023-12-21 to 2025-01-06) is built. Commissioner Nichols's class is likewise confirmed by the clerk's sheet (next election May 2028): the January 2025 - January 2029 class stands and the 'January 2028' figure is superseded.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Klamath County Clerk confirmation of the 2024 DA election's term and of Nichols's class.</t>
+          <t>Done.</t>
         </is>
       </c>
     </row>
@@ -16244,7 +16271,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Research item</t>
+          <t>Research item -- PARTIALLY RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -16254,12 +16281,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Leriche won the certified May 2024 primary (3,467), but a June 2025 Board agenda carries DA applicant presentations -- a vacancy being filled by appointment. Whether Leriche ever served, and who holds the office now, is undocumented in the sources read. Contest + candidacy only (the pass's one new winner-not-seated warning).</t>
+          <t>Research step: Leriche DID serve -- re-elected May 2024, sworn in January 2025, then resigned effective February 2, 2025 (Governor's vacancy announcement). The Governor appointed Leriche himself as acting DA; he served as acting DA through the county's June 2025 applicant interviews. His elected span (2025-01-06 to 2025-02-02) and an open acting span (from February 2025) are built, clearing the winner-not-seated warning. Still undocumented: whether a permanent appointment ever followed the Governor's two application rounds (February and May 2025). Eric Nisley, sole filer for the May 2026 primary, is NOT seated -- no source read confirms he took office.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Jefferson County sources / clerk: Leriche's service and the appointed successor's identity and date.</t>
+          <t>Verify the permanent holder from a certified May 2026 abstract or a Governor's appointment announcement; seat Nisley only on that documentation.</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16346,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Forward watch -- January 2027</t>
+          <t>Forward watch -- January 2027 (appointment ANNOUNCED)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -16329,12 +16356,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>An October 2026 county meeting report says DA Nelson expects to leave for a circuit-court judgeship (District 6) in early January 2027.</t>
+          <t>Updated 2026-10-25: DA Justin W. Nelson's move is no longer expected -- it is announced. Governor Kotek appointed him to the 6th Judicial District (announced September 22, 2026), effective January 1, 2027, succeeding a retiring Judge Collins.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify in January 2027; if he goes, end his DA membership, model the successor, and check the District 6 circuit vacancy against the circuit research queue.</t>
+          <t>In January 2027: end Nelson's DA membership (2027-01-01), build his circuit membership, end the District 6 Collins membership, and model Nelson's DA successor when documented.</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16371,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Verification owed</t>
+          <t>Verification owed -- RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -16354,12 +16381,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>An October 21, 2026 report outside county sources says Harney County Judge Hart resigned; unverified, and he is modeled as holding. Wallowa's third seat: Commissioner Roberts died in office July 30, 2025 (ended membership built); her successor is reported in meeting coverage as Cody Lathrop but is not verified on a county page.</t>
+          <t>Harney: Judge Bill Hart's resignation was read and accepted unanimously at the October 21, 2026 County Court meeting, effective immediately (his letter is quoted verbatim in the meeting account; the county minutes PDF was not yet posted) -- his membership is ended 2026-10-21 and the post is vacant. Wallowa: the earlier premise was wrong -- Roberts's died-in-office end (July 30, 2025) is CORRECT (she had announced retirement in May but died before it took effect). The interim appointee was Mike Hayward (appointed August 4, 2025), not Lathrop; Cody Lathrop was ELECTED at the May 19, 2026 primary to the two-year unexpired term and sworn in July 1, 2026. Both memberships are built. Note: Wallowa's seats are in fact numbered (this is Position 2) although the repo models one unnumbered post -- flagged for Walter.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>County sources for both; amend on documentation.</t>
+          <t>Done (Wallowa numbering question left for Walter).</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16396,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Research items (county successions)</t>
+          <t>Research items (county successions) -- RESOLVED 2026-10-25</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -16379,12 +16406,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Josephine's Martin and Richardson were appointed in January 2026 to vacant seats (dates/manner from county sources are summary-grade); Curry's Coker filled Alcorn's seat on an undocumented date and manner; Lane's elected Sheriff Harrold resigned in 2025 on an undocumented date (successor Wilkerson is built as appointed).</t>
+          <t>Josephine: Martin (Position 2) and Richardson (Position 1) were appointed February 18, 2026 -- not January -- by a Temporary Board of Other Elective Administrative Officers under ORS 236.215 (the Board of Commissioners lacked a quorum: Blech resigned, Barnett recalled), 6-0; both membership starts corrected. Curry: Lynn Coker was APPOINTED to Seat #1 for a term beginning May 2, 2025 (Emergency Meeting Minutes, April 23, 2025); his record corrected from 'succeeded' with no start. Lane: Sheriff Cliff Harrold (county sources say 'Cliff', not Clifton) announced retirement May 1, 2025 and left May 16, 2025 -- his elected membership is built (end only; his election/start undocumented). Wilkerson's service is split: acting from May 16, 2025, appointed June 11, 2025 (Board Order 25-06-11-01).</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>County minutes/orders for the exact instruments and dates; amend the records when documented.</t>
+          <t>Done.</t>
         </is>
       </c>
     </row>
